--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AD368FA-F073-49CD-94F9-A7957C595CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AEE7ACC-46C1-4570-AB32-46DB55156982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="13" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="12" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="11" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="10" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="9" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EA46BCE-EA61-7705-B0DD-AD98138E89FB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B3827F8-4EC0-614C-0EB5-1B3698D6E45A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73690E79-B422-F0D4-66DE-6771BBAFE69A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB6C20C4-206B-4AFE-3764-FB36501AB0B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177A154C-F4B5-4DCF-AB61-CEC731EB1B0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F0012-8994-42DC-BF98-403FA390EF52}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A38BD4-D1F8-4D11-83B5-8968B9F37536}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC7B8C1-5984-49A5-8860-43F20898E19C}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7761695-EFD2-4BF6-917B-E6D8F0D6C453}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05DC2E25-A3F5-415D-8484-E84ACB71BCB1}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A4089CA-4717-4095-8543-C16AE3460C27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DE7AD8-399A-4A04-ABBC-CAA5009226BD}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FBB16D-2244-4F65-881E-7893A5D71607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EEDCDD-13EB-4A23-ABDD-EB284EA0CEE3}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -67666,7 +67666,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q892">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="893" spans="1:25" x14ac:dyDescent="0.25">
@@ -67701,7 +67701,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q893">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="894" spans="1:25" x14ac:dyDescent="0.25">
@@ -67736,7 +67736,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q894">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="895" spans="1:25" x14ac:dyDescent="0.25">
@@ -81112,7 +81112,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1198">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1199" spans="1:17" x14ac:dyDescent="0.25">
@@ -81147,7 +81147,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1199">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1200" spans="1:17" x14ac:dyDescent="0.25">
@@ -81182,7 +81182,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1200">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1201" spans="1:17" x14ac:dyDescent="0.25">
@@ -81572,7 +81572,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1209">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
@@ -81607,7 +81607,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1210">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
@@ -81642,7 +81642,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1211">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1212" spans="1:17" x14ac:dyDescent="0.25">

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AEE7ACC-46C1-4570-AB32-46DB55156982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23100E6A-4139-4E39-96FC-618BF0BEAC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B3827F8-4EC0-614C-0EB5-1B3698D6E45A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F85891-0C3D-6EDF-19E1-478A41BC4415}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB6C20C4-206B-4AFE-3764-FB36501AB0B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12496F00-5D03-E757-5A75-3C113735529A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F0012-8994-42DC-BF98-403FA390EF52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F81D213-AC7A-4CFB-A53E-5E5FF9CEA782}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC7B8C1-5984-49A5-8860-43F20898E19C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CF51F7-FD48-42DA-B08B-F5949006E96A}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05DC2E25-A3F5-415D-8484-E84ACB71BCB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC4564B-682D-4FD1-AD29-361236FAAAC7}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DE7AD8-399A-4A04-ABBC-CAA5009226BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8352011-37FB-48F2-A837-DDFEF34E2A76}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EEDCDD-13EB-4A23-ABDD-EB284EA0CEE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA50D6F-2930-4F7C-A6E3-045F6CC647CC}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -67666,7 +67666,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q892">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="893" spans="1:25" x14ac:dyDescent="0.25">
@@ -67701,7 +67701,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q893">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="894" spans="1:25" x14ac:dyDescent="0.25">
@@ -67736,7 +67736,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q894">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="895" spans="1:25" x14ac:dyDescent="0.25">
@@ -81572,7 +81572,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1209">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
@@ -81607,7 +81607,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1210">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
@@ -81642,7 +81642,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1211">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1212" spans="1:17" x14ac:dyDescent="0.25">

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23100E6A-4139-4E39-96FC-618BF0BEAC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F166530F-689F-406D-BBC8-F41C02CA7D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="28" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="27" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="26" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="25" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="24" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F85891-0C3D-6EDF-19E1-478A41BC4415}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2018FD0D-F65B-C385-1F38-571A1FCCD2A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12496F00-5D03-E757-5A75-3C113735529A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26920A82-85F3-9029-A2BB-374D32D5DA21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F81D213-AC7A-4CFB-A53E-5E5FF9CEA782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E093862F-B49B-4F10-AAB1-88F2E22392ED}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7CF51F7-FD48-42DA-B08B-F5949006E96A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFAB767-D087-4CEA-88A3-2E7C16923319}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC4564B-682D-4FD1-AD29-361236FAAAC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83210EA9-F815-4278-B950-4A873ECF9238}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8352011-37FB-48F2-A837-DDFEF34E2A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE219FA-A0FA-4E8D-9748-78A5BF4ACC86}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA50D6F-2930-4F7C-A6E3-045F6CC647CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903BE2F1-8010-45A1-B8BB-6FA16A144655}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -67666,7 +67666,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q892">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="893" spans="1:25" x14ac:dyDescent="0.25">
@@ -67701,7 +67701,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q893">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="894" spans="1:25" x14ac:dyDescent="0.25">
@@ -67736,7 +67736,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q894">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="895" spans="1:25" x14ac:dyDescent="0.25">
@@ -81572,7 +81572,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1209">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
@@ -81607,7 +81607,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1210">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
@@ -81642,7 +81642,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1211">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1212" spans="1:17" x14ac:dyDescent="0.25">

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F166530F-689F-406D-BBC8-F41C02CA7D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C732B99-F221-4D33-993E-E318BEC71E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="28" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="27" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="26" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="25" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="24" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2018FD0D-F65B-C385-1F38-571A1FCCD2A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A7163E-5995-3BD5-C79F-383405095A23}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26920A82-85F3-9029-A2BB-374D32D5DA21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B87981E-1ABB-A7F9-1521-67B89264FACD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E093862F-B49B-4F10-AAB1-88F2E22392ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C91D0E5-9990-4FAD-B1B2-8AB2BAAA7719}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFAB767-D087-4CEA-88A3-2E7C16923319}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CA906E-F7A3-49AD-904D-EFDA60EC4C4B}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83210EA9-F815-4278-B950-4A873ECF9238}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF75749-E2E4-4481-A636-D2F5BD07ABAF}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE219FA-A0FA-4E8D-9748-78A5BF4ACC86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD97298-2AD9-490F-9633-6838DB1A19E0}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903BE2F1-8010-45A1-B8BB-6FA16A144655}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A7B315-3257-4061-952B-5A4B92F91468}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C732B99-F221-4D33-993E-E318BEC71E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27A46317-2BAE-494B-BDA3-512DB9AF7398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="53" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="52" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="51" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="50" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="49" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A7163E-5995-3BD5-C79F-383405095A23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDA67360-91FA-A779-6039-4EC0DBEBB889}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B87981E-1ABB-A7F9-1521-67B89264FACD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C686F150-F944-2B4E-0D51-DBCFE97B3870}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C91D0E5-9990-4FAD-B1B2-8AB2BAAA7719}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B75172D-465C-47EC-B019-620AAF39BE79}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CA906E-F7A3-49AD-904D-EFDA60EC4C4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87EAEE7D-25E1-4B1E-AE1F-7363FBC044AF}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF75749-E2E4-4481-A636-D2F5BD07ABAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB11826D-D19F-4FAB-8C4E-508FAD43B840}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD97298-2AD9-490F-9633-6838DB1A19E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972D268A-52F3-4D89-A1EC-AA438BE7FC4C}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A7B315-3257-4061-952B-5A4B92F91468}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDF114F-D1A7-4BBD-9B61-32D4949EF8BE}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -81112,7 +81112,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1198">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1199" spans="1:17" x14ac:dyDescent="0.25">
@@ -81147,7 +81147,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1199">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1200" spans="1:17" x14ac:dyDescent="0.25">
@@ -81182,7 +81182,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1200">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1201" spans="1:17" x14ac:dyDescent="0.25">
@@ -81572,7 +81572,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1209">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
@@ -81607,7 +81607,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1210">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
@@ -81642,7 +81642,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1211">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1212" spans="1:17" x14ac:dyDescent="0.25">

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27A46317-2BAE-494B-BDA3-512DB9AF7398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A8E1E5F-19DC-4661-A4A7-73C11DB946C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="53" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="52" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="51" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="50" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="49" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="58" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="57" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="56" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="55" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="54" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDA67360-91FA-A779-6039-4EC0DBEBB889}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AA1D159-D070-949A-E1C0-FFE8CE2B63B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C686F150-F944-2B4E-0D51-DBCFE97B3870}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA5F9202-C8B1-87E9-E6FF-CFC6997EBD47}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B75172D-465C-47EC-B019-620AAF39BE79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BC6927-8DD9-45BC-B36A-20BB77BFED9C}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87EAEE7D-25E1-4B1E-AE1F-7363FBC044AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967784BA-07DF-4AB8-910D-A40F98D861A8}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB11826D-D19F-4FAB-8C4E-508FAD43B840}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60A34B2-082E-41D6-AD0D-53446CA9AFFF}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972D268A-52F3-4D89-A1EC-AA438BE7FC4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB60839-4A9D-4A8F-AE61-A7C9F60E96C4}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDF114F-D1A7-4BBD-9B61-32D4949EF8BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C07F68D-9B6D-43A8-A5F0-69184EC696C9}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -81112,7 +81112,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1198">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1199" spans="1:17" x14ac:dyDescent="0.25">
@@ -81147,7 +81147,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1199">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1200" spans="1:17" x14ac:dyDescent="0.25">
@@ -81182,7 +81182,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1200">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1201" spans="1:17" x14ac:dyDescent="0.25">
@@ -81572,7 +81572,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1209">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
@@ -81607,7 +81607,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1210">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
@@ -81642,7 +81642,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1211">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1212" spans="1:17" x14ac:dyDescent="0.25">

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A8E1E5F-19DC-4661-A4A7-73C11DB946C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7941002-F1E9-49BC-93DA-F27631C6BAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="58" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="57" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="56" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="55" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="54" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="63" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="62" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="61" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="60" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="59" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AA1D159-D070-949A-E1C0-FFE8CE2B63B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{371F713C-0866-0E7E-9499-E345A9E84935}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA5F9202-C8B1-87E9-E6FF-CFC6997EBD47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47F2E549-0F61-2A35-B892-3B4475A8BF18}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BC6927-8DD9-45BC-B36A-20BB77BFED9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB3D96F9-2E8E-491E-BFC4-F6FC67BB70AB}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967784BA-07DF-4AB8-910D-A40F98D861A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B58AAE98-DABF-4E14-96BA-002DF3534174}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60A34B2-082E-41D6-AD0D-53446CA9AFFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D0CC34-251D-4956-AA2C-1BD8C4F6B382}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB60839-4A9D-4A8F-AE61-A7C9F60E96C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC76049B-9B2C-4D56-968B-A5902FA77AA7}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C07F68D-9B6D-43A8-A5F0-69184EC696C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5050B3E-5BCC-4739-A6AD-736438CC2210}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -81112,7 +81112,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1198">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1199" spans="1:17" x14ac:dyDescent="0.25">
@@ -81147,7 +81147,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1199">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1200" spans="1:17" x14ac:dyDescent="0.25">
@@ -81182,7 +81182,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1200">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1201" spans="1:17" x14ac:dyDescent="0.25">

--- a/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
+++ b/VerveStacks_JPN_grids_kan/source_data/VerveStacks_JPN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Himanshu\GitHub\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7941002-F1E9-49BC-93DA-F27631C6BAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A470FBD4-2FA2-4775-9A5D-EE691C4531F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="63" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="62" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="61" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="60" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="59" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="68" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="67" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="66" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="65" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="64" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -6659,7 +6659,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{371F713C-0866-0E7E-9499-E345A9E84935}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D967B19-EB19-111D-E7EF-43462491843E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6714,7 +6714,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47F2E549-0F61-2A35-B892-3B4475A8BF18}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7157C065-8F65-D932-095A-6146C7BBF180}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7065,7 +7065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB3D96F9-2E8E-491E-BFC4-F6FC67BB70AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6E0DC7-D548-4518-A8A0-1AD1DFC7F2C0}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10193,7 +10193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B58AAE98-DABF-4E14-96BA-002DF3534174}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54306B00-1940-48DD-8E99-7C78DCDD2834}">
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11065,7 +11065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D0CC34-251D-4956-AA2C-1BD8C4F6B382}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B4897DB-AC38-4D8D-B06F-7210E7416EA7}">
   <dimension ref="B2:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -18475,7 +18475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC76049B-9B2C-4D56-968B-A5902FA77AA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160A2443-C4B9-4159-86EE-5AF14AA34670}">
   <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -19161,7 +19161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5050B3E-5BCC-4739-A6AD-736438CC2210}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B38344-035A-4FE3-90A0-5BF90ECA9CB3}">
   <dimension ref="A1:Y1337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -67666,7 +67666,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q892">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="893" spans="1:25" x14ac:dyDescent="0.25">
@@ -67701,7 +67701,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q893">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="894" spans="1:25" x14ac:dyDescent="0.25">
@@ -67736,7 +67736,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q894">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="895" spans="1:25" x14ac:dyDescent="0.25">
@@ -81572,7 +81572,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1209">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
@@ -81607,7 +81607,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1210">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
@@ -81642,7 +81642,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q1211">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1212" spans="1:17" x14ac:dyDescent="0.25">
